--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t xml:space="preserve">OrderId </t>
   </si>
@@ -466,7 +466,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>46128.0</v>
+        <v>46127.0</v>
       </c>
       <c r="C12" s="1">
         <v>21002.0</v>
@@ -518,21 +518,21 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>46133.0</v>
+        <v>46132.0</v>
       </c>
       <c r="C17" s="1">
-        <v>21002.0</v>
+        <v>21502.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>46134.0</v>
+        <v>46133.0</v>
       </c>
       <c r="C18" s="1">
         <v>21002.0</v>
@@ -540,31 +540,42 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>46135.0</v>
+        <v>46134.0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>21002.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>46136.0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>21002.0</v>
+        <v>46135.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46136.0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>21002.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>46137.0</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C22" s="1">
         <v>21002.0</v>
       </c>
     </row>
